--- a/artfynd/A 32985-2023 artfynd.xlsx
+++ b/artfynd/A 32985-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32985-2023 artfynd.xlsx
+++ b/artfynd/A 32985-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,136 +808,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>112564182</v>
-      </c>
-      <c r="B3" t="n">
-        <v>104016</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>340</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Ryl</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Chimaphila umbellata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Näset, 450 m SSV om, Sm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>542782</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6404993</v>
-      </c>
-      <c r="S3" t="n">
-        <v>50</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Vimmerby</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Södra Vi</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Hf-Vim-1025</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sören Mjösberg</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Åke Rühling</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Via Åke Rühling</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 32985-2023 artfynd.xlsx
+++ b/artfynd/A 32985-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>130225</v>
       </c>
       <c r="B2" t="n">
-        <v>103225</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105751</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542781.8277125754</v>
+        <v>542782</v>
       </c>
       <c r="R2" t="n">
-        <v>6404992.839413385</v>
+        <v>6404993</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -762,19 +757,9 @@
           <t>2007-06-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-06-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 32985-2023 artfynd.xlsx
+++ b/artfynd/A 32985-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130225</v>
       </c>
       <c r="B2" t="n">
-        <v>105751</v>
+        <v>105754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32985-2023 artfynd.xlsx
+++ b/artfynd/A 32985-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130225</v>
       </c>
       <c r="B2" t="n">
-        <v>105754</v>
+        <v>105783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32985-2023 artfynd.xlsx
+++ b/artfynd/A 32985-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130225</v>
       </c>
       <c r="B2" t="n">
-        <v>105783</v>
+        <v>105795</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32985-2023 artfynd.xlsx
+++ b/artfynd/A 32985-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130225</v>
       </c>
       <c r="B2" t="n">
-        <v>105795</v>
+        <v>105796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32985-2023 artfynd.xlsx
+++ b/artfynd/A 32985-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130225</v>
       </c>
       <c r="B2" t="n">
-        <v>105796</v>
+        <v>105801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32985-2023 artfynd.xlsx
+++ b/artfynd/A 32985-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130225</v>
       </c>
       <c r="B2" t="n">
-        <v>105801</v>
+        <v>105805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32985-2023 artfynd.xlsx
+++ b/artfynd/A 32985-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130225</v>
       </c>
       <c r="B2" t="n">
-        <v>105805</v>
+        <v>105807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32985-2023 artfynd.xlsx
+++ b/artfynd/A 32985-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130225</v>
       </c>
       <c r="B2" t="n">
-        <v>105807</v>
+        <v>105817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32985-2023 artfynd.xlsx
+++ b/artfynd/A 32985-2023 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>130225</v>
       </c>
       <c r="B2" t="n">
-        <v>105817</v>
+        <v>106204</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">

--- a/artfynd/A 32985-2023 artfynd.xlsx
+++ b/artfynd/A 32985-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,8 +802,16 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130225</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>